--- a/final.xlsx
+++ b/final.xlsx
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7124616291535962</v>
+        <v>0.7118189073496337</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8259631923194061</v>
+        <v>0.8273348519362188</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7779130684504729</v>
+        <v>0.7790460730814394</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8901482058874304</v>
+        <v>0.8899463639765498</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6448943393161698</v>
+        <v>0.6449399922570654</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8162009212546611</v>
+        <v>0.8170323928944617</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6851524603368926</v>
+        <v>0.6844758918735701</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8531213216637982</v>
+        <v>0.8530497692403641</v>
       </c>
     </row>
     <row r="4">
@@ -509,16 +509,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.619850399793655</v>
+        <v>0.6179581795817959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7476790231931042</v>
+        <v>0.7491962805449434</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7427159472170631</v>
+        <v>0.7407100644699141</v>
       </c>
       <c r="F4" t="n">
-        <v>0.808538709829299</v>
+        <v>0.8081077709866533</v>
       </c>
     </row>
     <row r="5">
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6133492987468731</v>
+        <v>0.6131407533276692</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8169556437573985</v>
+        <v>0.8179501385041552</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6556538713858265</v>
+        <v>0.6539196940726577</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8545965797031696</v>
+        <v>0.8540476487464138</v>
       </c>
     </row>
     <row r="6">
@@ -553,16 +553,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6431791899009814</v>
+        <v>0.6423696615774291</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8798586183738218</v>
+        <v>0.8794044321329638</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5923244669898733</v>
+        <v>0.5911096156721998</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8894058685974062</v>
+        <v>0.8876886615941123</v>
       </c>
     </row>
     <row r="7">
@@ -575,16 +575,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6232497085582305</v>
+        <v>0.6231487708286633</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8405107907944487</v>
+        <v>0.8406507500528207</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6964180638877804</v>
+        <v>0.6947547353084023</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8788750372738067</v>
+        <v>0.8778346014718721</v>
       </c>
     </row>
     <row r="8">
@@ -597,16 +597,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7053807166085606</v>
+        <v>0.7041602465331277</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8533186405224359</v>
+        <v>0.8538734516237025</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8151013153864118</v>
+        <v>0.81404360107192</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8997692947534174</v>
+        <v>0.8993887988025445</v>
       </c>
     </row>
     <row r="9">
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6829474787469431</v>
+        <v>0.6825869262865091</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8204120088615009</v>
+        <v>0.8219806926348477</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7580882015510991</v>
+        <v>0.7588428845626544</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8658896276804444</v>
+        <v>0.8654359486092055</v>
       </c>
     </row>
     <row r="10">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6260773384174297</v>
+        <v>0.6265875785066295</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6508938960106033</v>
+        <v>0.6525466139317138</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6966719809545091</v>
+        <v>0.6963842333954068</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6696054992597552</v>
+        <v>0.6701384557814644</v>
       </c>
     </row>
     <row r="11">
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6311572122762965</v>
+        <v>0.6331731136034179</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8127527271646405</v>
+        <v>0.8149410595085925</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6709951028619257</v>
+        <v>0.6706680126404494</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8276474865683509</v>
+        <v>0.8272795309966321</v>
       </c>
     </row>
     <row r="12">
@@ -685,16 +685,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6583039366932302</v>
+        <v>0.6592795186371806</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8505488854039023</v>
+        <v>0.8522785768357305</v>
       </c>
       <c r="E12" t="n">
-        <v>0.81325018475516</v>
+        <v>0.8143000250438266</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8999325147918158</v>
+        <v>0.899239116876637</v>
       </c>
     </row>
     <row r="13">
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6020350721962456</v>
+        <v>0.6021140878439949</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7222357954341313</v>
+        <v>0.7238119746097099</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7388679152775053</v>
+        <v>0.7369499063670414</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7618180201200087</v>
+        <v>0.7619059498565548</v>
       </c>
     </row>
     <row r="14">
@@ -729,16 +729,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6606281008260538</v>
+        <v>0.6623842246788171</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8084895922663132</v>
+        <v>0.8098529521534674</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7463018194766141</v>
+        <v>0.7456107031315946</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8560451575439567</v>
+        <v>0.8560808282399899</v>
       </c>
     </row>
     <row r="15">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.640707027524746</v>
+        <v>0.6423446105428796</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8703177166469085</v>
+        <v>0.8709259947936034</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7912404103214743</v>
+        <v>0.7913708127975942</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8745769095959781</v>
+        <v>0.8744418111513034</v>
       </c>
     </row>
     <row r="16">
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6299339390348729</v>
+        <v>0.6300500287049947</v>
       </c>
       <c r="D16" t="n">
-        <v>0.710612747814409</v>
+        <v>0.7123809523809524</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5094784954293422</v>
+        <v>0.5053494352098448</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7482461692989385</v>
+        <v>0.747623799426219</v>
       </c>
     </row>
     <row r="17">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6117957559408945</v>
+        <v>0.6114271661611609</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7790381472107982</v>
+        <v>0.7802486622599936</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6965667895334889</v>
+        <v>0.6955769413103252</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8361443451057529</v>
+        <v>0.8352376200573778</v>
       </c>
     </row>
   </sheetData>
